--- a/utils/monday_sprint_sprint_2025-19.xlsx
+++ b/utils/monday_sprint_sprint_2025-19.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="288">
   <si>
     <t>Ticket</t>
   </si>
@@ -231,6 +231,9 @@
     <t>31/01/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
@@ -651,7 +654,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -774,7 +777,7 @@
     <t>25/06/2025</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>32141</t>
@@ -2174,7 +2177,7 @@
         <v>71</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>20</v>
@@ -2183,12 +2186,12 @@
         <v>40</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2200,10 +2203,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>24</v>
@@ -2232,7 +2235,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2244,10 +2247,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>24</v>
@@ -2276,7 +2279,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2288,10 +2291,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2320,7 +2323,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2332,10 +2335,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2364,7 +2367,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2376,10 +2379,10 @@
         <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2388,10 +2391,10 @@
         <v>69</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>17</v>
@@ -2403,12 +2406,12 @@
         <v>29</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2420,10 +2423,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2452,7 +2455,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2464,10 +2467,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>24</v>
@@ -2496,7 +2499,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2508,10 +2511,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>24</v>
@@ -2540,7 +2543,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2552,10 +2555,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2584,7 +2587,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2596,10 +2599,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2628,7 +2631,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2640,10 +2643,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2672,7 +2675,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2684,10 +2687,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>19</v>
@@ -2716,7 +2719,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2728,10 +2731,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2760,7 +2763,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2772,10 +2775,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2804,7 +2807,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2816,10 +2819,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2848,7 +2851,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2860,10 +2863,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2892,7 +2895,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2904,10 +2907,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2936,7 +2939,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2948,10 +2951,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2980,7 +2983,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2992,10 +2995,10 @@
         <v>66</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -3007,10 +3010,10 @@
         <v>70</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3019,12 +3022,12 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3036,10 +3039,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -3068,7 +3071,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3080,10 +3083,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>24</v>
@@ -3112,7 +3115,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3124,10 +3127,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3156,7 +3159,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3168,10 +3171,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>19</v>
@@ -3200,7 +3203,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3212,10 +3215,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3244,7 +3247,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3256,7 +3259,7 @@
         <v>66</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>17</v>
@@ -3265,13 +3268,13 @@
         <v>24</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>17</v>
@@ -3283,12 +3286,12 @@
         <v>29</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3300,10 +3303,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3332,7 +3335,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3344,10 +3347,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3376,7 +3379,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3388,10 +3391,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3420,22 +3423,22 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>24</v>
@@ -3453,7 +3456,7 @@
         <v>17</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>21</v>
@@ -3464,7 +3467,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3476,7 +3479,7 @@
         <v>66</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>17</v>
@@ -3485,13 +3488,13 @@
         <v>24</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>17</v>
@@ -3503,12 +3506,12 @@
         <v>29</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3520,10 +3523,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3552,7 +3555,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3564,10 +3567,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3596,7 +3599,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3608,10 +3611,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3640,7 +3643,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3652,10 +3655,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>24</v>
@@ -3684,7 +3687,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3696,10 +3699,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3728,7 +3731,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3740,10 +3743,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3772,7 +3775,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3784,10 +3787,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>24</v>
@@ -3816,7 +3819,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3828,10 +3831,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>24</v>
@@ -3860,7 +3863,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3872,10 +3875,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3904,7 +3907,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3916,10 +3919,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3948,22 +3951,22 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>19</v>
@@ -3992,7 +3995,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4004,10 +4007,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -4036,7 +4039,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4048,10 +4051,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -4080,7 +4083,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4092,10 +4095,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4124,7 +4127,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4136,10 +4139,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4168,7 +4171,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4180,10 +4183,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4212,22 +4215,22 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>24</v>
@@ -4245,7 +4248,7 @@
         <v>17</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>21</v>
@@ -4256,7 +4259,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4268,10 +4271,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>19</v>
@@ -4289,7 +4292,7 @@
         <v>17</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>21</v>
@@ -4300,7 +4303,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4312,10 +4315,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>19</v>
@@ -4344,7 +4347,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4356,10 +4359,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4388,37 +4391,37 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>66</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>34</v>
@@ -4427,12 +4430,12 @@
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4444,10 +4447,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4476,7 +4479,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4488,10 +4491,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4532,10 +4535,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4564,7 +4567,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4576,10 +4579,10 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
@@ -4608,7 +4611,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4620,10 +4623,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4652,7 +4655,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4664,10 +4667,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>19</v>
@@ -4696,7 +4699,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4708,10 +4711,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4740,7 +4743,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4752,10 +4755,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4784,7 +4787,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4796,10 +4799,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>24</v>
@@ -4828,7 +4831,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4840,10 +4843,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4872,7 +4875,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4884,25 +4887,25 @@
         <v>66</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>34</v>
@@ -4911,12 +4914,12 @@
         <v>29</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4928,10 +4931,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4960,7 +4963,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4972,22 +4975,22 @@
         <v>66</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>17</v>
@@ -4999,27 +5002,27 @@
         <v>53</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -5060,10 +5063,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5104,10 +5107,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5136,7 +5139,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5148,10 +5151,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5180,7 +5183,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5192,10 +5195,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5236,10 +5239,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5257,7 +5260,7 @@
         <v>17</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M90" s="2" t="s">
         <v>26</v>
@@ -5268,7 +5271,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5280,10 +5283,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5312,7 +5315,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5324,10 +5327,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>19</v>
@@ -5356,7 +5359,7 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>15</v>
@@ -5368,10 +5371,10 @@
         <v>17</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>19</v>
@@ -5400,7 +5403,7 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>15</v>
@@ -5412,10 +5415,10 @@
         <v>17</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>19</v>
@@ -5444,7 +5447,7 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>15</v>
@@ -5456,10 +5459,10 @@
         <v>17</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>19</v>
@@ -5477,7 +5480,7 @@
         <v>17</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M95" s="2" t="s">
         <v>21</v>
@@ -5488,7 +5491,7 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>15</v>
@@ -5500,10 +5503,10 @@
         <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>19</v>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>15</v>
@@ -5544,10 +5547,10 @@
         <v>17</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>19</v>
@@ -5576,7 +5579,7 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>15</v>
@@ -5588,10 +5591,10 @@
         <v>17</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>19</v>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>15</v>
@@ -5632,25 +5635,25 @@
         <v>66</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>37</v>
@@ -5659,12 +5662,12 @@
         <v>29</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>15</v>
@@ -5676,10 +5679,10 @@
         <v>66</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>24</v>
@@ -5688,10 +5691,10 @@
         <v>69</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>17</v>
@@ -5703,12 +5706,12 @@
         <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>15</v>
@@ -5720,10 +5723,10 @@
         <v>17</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>19</v>
@@ -5764,10 +5767,10 @@
         <v>17</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>24</v>
@@ -5807,23 +5810,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5831,16 +5834,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5859,7 +5862,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5880,7 +5883,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5911,12 +5914,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B2">
         <v>101</v>
@@ -5940,25 +5943,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5975,13 +5978,13 @@
         <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5996,7 +5999,7 @@
         <v>26</v>
       </c>
       <c r="Q10">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -6013,7 +6016,7 @@
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K11">
         <v>101</v>
@@ -6045,7 +6048,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -6054,18 +6057,18 @@
         <v>53</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -6085,13 +6088,13 @@
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6106,12 +6109,12 @@
         <v>40</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -6119,7 +6122,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6127,7 +6130,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6135,7 +6138,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6146,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6154,16 +6157,16 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -6182,49 +6185,49 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>113</v>
+        <v>184</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>184</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
@@ -6233,63 +6236,63 @@
         <v>332</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>255</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-19.xlsx
+++ b/utils/monday_sprint_sprint_2025-19.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="298">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,27 +63,45 @@
     <t>31794</t>
   </si>
   <si>
-    <t>Sprint 2025-19</t>
+    <t>Setor não informado</t>
   </si>
   <si>
     <t>Melhoria</t>
   </si>
   <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>09/09/2025</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Inclusão de romaneios manualmente no Recibo de Embarque</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
     <t>Implantação</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>Setembro</t>
+  </si>
+  <si>
     <t>24641</t>
   </si>
   <si>
@@ -90,36 +111,60 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>01/03/2024</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
     <t>Semana 1</t>
   </si>
   <si>
+    <t>Março</t>
+  </si>
+  <si>
     <t>32974</t>
   </si>
   <si>
     <t>Projeto BI IROG SPA - Criar tela de cadastro de metas para BI</t>
   </si>
   <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>Julho</t>
+  </si>
+  <si>
     <t>32425</t>
   </si>
   <si>
     <t>Precisamos que SPS conecte ao WMS</t>
   </si>
   <si>
+    <t>11/08/2025</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
     <t>33657</t>
   </si>
   <si>
     <t>ABERTURA DE SALDO SETOR 597 X MOVIMENTAÇÃO SETOR 7299</t>
   </si>
   <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
+    <t>Aberto</t>
+  </si>
+  <si>
     <t>33594</t>
   </si>
   <si>
@@ -135,6 +180,9 @@
     <t>Planilhão via Qlik sense</t>
   </si>
   <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
@@ -147,6 +195,9 @@
     <t>Painel ajustagem</t>
   </si>
   <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
     <t>33820</t>
   </si>
   <si>
@@ -174,6 +225,9 @@
     <t>Projeto BI IROG SPA - Cópia  de metas de ano/mês</t>
   </si>
   <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
@@ -228,10 +282,7 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>25418</t>
@@ -246,12 +297,18 @@
     <t>SISTEMA DE ENSAIOS MECÂNICOS DE PEÇA - Analise</t>
   </si>
   <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
     <t>32077</t>
   </si>
   <si>
     <t>alterar informações de romaneio e quantidade (copy)</t>
   </si>
   <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
     <t>31270</t>
   </si>
   <si>
@@ -264,153 +321,141 @@
     <t>Melhoria WMS - Conferencia e Carregamento</t>
   </si>
   <si>
-    <t>Boa tarde Precisamos que as etapas de Saida Deposito do WMS possam ser revertidas e editadas após o processo "finalizado". * Uma vez realizado o carregamento, que seja possível , voltar e excluir NF / itens. Sugestão: selecionar os romaneios (já vinculados a NF) e excluir, voltando os Romaneios a St</t>
+    <t>33492</t>
+  </si>
+  <si>
+    <t>LOG DE ALTERAÇÕES APONTAMNETO ELETRONICO</t>
+  </si>
+  <si>
+    <t>32723</t>
+  </si>
+  <si>
+    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
+  </si>
+  <si>
+    <t>32588</t>
+  </si>
+  <si>
+    <t>Baixa de Estoque de Embalagem Expedição</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>33441</t>
+  </si>
+  <si>
+    <t>Melhoria de copia de analise e processos</t>
+  </si>
+  <si>
+    <t>26571</t>
+  </si>
+  <si>
+    <t>Retirar de peças do deposito para versão WMS</t>
+  </si>
+  <si>
+    <t>33571</t>
+  </si>
+  <si>
+    <t>Revisão de Checklist CPC</t>
+  </si>
+  <si>
+    <t>33333</t>
+  </si>
+  <si>
+    <t>Verificar apontamentos com origem na solda - Não permitir Alterar</t>
+  </si>
+  <si>
+    <t>33896</t>
+  </si>
+  <si>
+    <t>MPO's eletrônicas acabamento</t>
+  </si>
+  <si>
+    <t>32685</t>
+  </si>
+  <si>
+    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
+  </si>
+  <si>
+    <t>33662</t>
+  </si>
+  <si>
+    <t>Controle de documentação de exportação</t>
+  </si>
+  <si>
+    <t>34073</t>
+  </si>
+  <si>
+    <t>HUB CHATBOT - FRONTEND</t>
+  </si>
+  <si>
+    <t>29476</t>
+  </si>
+  <si>
+    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
+  </si>
+  <si>
+    <t>31015</t>
+  </si>
+  <si>
+    <t>Conversão KB TOTO - Relatórios</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>33519</t>
+  </si>
+  <si>
+    <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
+  </si>
+  <si>
+    <t>Relação de aplicações WEB</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>33592</t>
+  </si>
+  <si>
+    <t>Opção para movimentar todas as sequências no setor</t>
+  </si>
+  <si>
+    <t>33445</t>
+  </si>
+  <si>
+    <t>PAINEL DE INFO PARADAS JATOS</t>
+  </si>
+  <si>
+    <t>24746</t>
+  </si>
+  <si>
+    <t>Integração de faturamentos com eventos</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Integração CRM - Tarefa para disparar integrações</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>22/05/2025</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>33492</t>
-  </si>
-  <si>
-    <t>LOG DE ALTERAÇÕES APONTAMNETO ELETRONICO</t>
-  </si>
-  <si>
-    <t>32723</t>
-  </si>
-  <si>
-    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
-  </si>
-  <si>
-    <t>32588</t>
-  </si>
-  <si>
-    <t>Baixa de Estoque de Embalagem Expedição</t>
-  </si>
-  <si>
-    <t>33441</t>
-  </si>
-  <si>
-    <t>Melhoria de copia de analise e processos</t>
-  </si>
-  <si>
-    <t>26571</t>
-  </si>
-  <si>
-    <t>Retirar de peças do deposito para versão WMS</t>
-  </si>
-  <si>
-    <t>33571</t>
-  </si>
-  <si>
-    <t>Revisão de Checklist CPC</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Verificar apontamentos com origem na solda - Não permitir Alterar</t>
-  </si>
-  <si>
-    <t>33896</t>
-  </si>
-  <si>
-    <t>MPO's eletrônicas acabamento</t>
-  </si>
-  <si>
-    <t>32685</t>
-  </si>
-  <si>
-    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
-  </si>
-  <si>
-    <t>33662</t>
-  </si>
-  <si>
-    <t>Controle de documentação de exportação</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>HUB CHATBOT - FRONTEND</t>
-  </si>
-  <si>
-    <t>29476</t>
-  </si>
-  <si>
-    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
-  </si>
-  <si>
-    <t>31015</t>
-  </si>
-  <si>
-    <t>Conversão KB TOTO - Relatórios</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>33519</t>
-  </si>
-  <si>
-    <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
-  </si>
-  <si>
-    <t>Relação de aplicações WEB</t>
-  </si>
-  <si>
-    <t>33592</t>
-  </si>
-  <si>
-    <t>Opção para movimentar todas as sequências no setor</t>
-  </si>
-  <si>
-    <t>33445</t>
-  </si>
-  <si>
-    <t>PAINEL DE INFO PARADAS JATOS</t>
-  </si>
-  <si>
-    <t>24746</t>
-  </si>
-  <si>
-    <t>Integração de faturamentos com eventos</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Integração CRM - Tarefa para disparar integrações</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
     <t>33516</t>
   </si>
   <si>
@@ -630,6 +675,9 @@
     <t>Publicar aplicações de apontamento (POSTMOVTO)</t>
   </si>
   <si>
+    <t>07/09/2025</t>
+  </si>
+  <si>
     <t>33921</t>
   </si>
   <si>
@@ -642,21 +690,6 @@
     <t>Consulta de divergências - Registro Pintura</t>
   </si>
   <si>
-    <t xml:space="preserve">Boa tarde, Visando uma melhoria no setor de pintura e uma adequação para ISO9001, o registro de pintura é hoje realizado manualmente pelo pintor, correndo assim, o risco do mesmo esquecer de preencher o documento ao final da atividade. A ideia seria inserir um registro digital, parecido com o que é </t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
     <t>32677</t>
   </si>
   <si>
@@ -675,9 +708,6 @@
     <t>Paulo Giovani da Cruz</t>
   </si>
   <si>
-    <t>17/06/2025</t>
-  </si>
-  <si>
     <t>30903</t>
   </si>
   <si>
@@ -762,6 +792,9 @@
     <t>32484</t>
   </si>
   <si>
+    <t>TI</t>
+  </si>
+  <si>
     <t>Teste integração MES - Sql Express (copy)</t>
   </si>
   <si>
@@ -771,10 +804,7 @@
     <t>Edson João Hammermeister</t>
   </si>
   <si>
-    <t>25/06/2025</t>
-  </si>
-  <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>32141</t>
@@ -786,6 +816,9 @@
     <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
   </si>
   <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
     <t>9986350423</t>
   </si>
   <si>
@@ -837,7 +870,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -855,7 +888,7 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Não</t>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Baixa</t>
@@ -1290,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N102"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1300,13 +1333,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1349,4449 +1384,4755 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="M15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="M16" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="J20" s="2" t="s">
+      <c r="M20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2" t="s">
+      <c r="O20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="2" t="s">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="M30" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L43" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I45" s="2" t="s">
+      <c r="M46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L45" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="2" t="s">
+      <c r="E50" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="M51" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N57" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L58" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="N58" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O58" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M75" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M79" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>17</v>
+        <v>220</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M81" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>210</v>
+        <v>21</v>
       </c>
       <c r="I82" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J82" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="L82" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N86" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M82" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A83" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L83" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M83" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N83" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A84" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L84" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A85" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L85" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N85" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A86" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L86" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M86" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N86" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M87" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M96" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>15</v>
+        <v>259</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="I99" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="J99" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K99" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M99" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="E100" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>17</v>
+        <v>267</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5807,23 +6148,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D2" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5831,16 +6172,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5851,20 +6192,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>18.62</v>
+        <v>248</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K22">
         <v>46</v>
@@ -5872,7 +6213,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K23">
         <v>14</v>
@@ -5880,7 +6221,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5911,12 +6252,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B2">
         <v>101</v>
@@ -5930,188 +6271,206 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>18.62</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N10">
         <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q10">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H11">
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>280</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="N11">
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E12">
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <v>81</v>
       </c>
+      <c r="J12" t="s">
+        <v>291</v>
+      </c>
+      <c r="K12">
+        <v>41</v>
+      </c>
       <c r="M12" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
       <c r="P13" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N14">
         <v>14</v>
       </c>
       <c r="P14" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="Q14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -6119,7 +6478,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6127,7 +6486,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6135,7 +6494,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -6146,7 +6505,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6154,142 +6513,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>238</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>228</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>347</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>183</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>184</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>254</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>255</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>216</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>217</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>248</v>
+        <v>57</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>313</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>249</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>127</v>
+        <v>63</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-19.xlsx
+++ b/utils/monday_sprint_sprint_2025-19.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="309">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>31794</t>
+    <t>10007327326</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,394 +87,418 @@
     <t>09/09/2025</t>
   </si>
   <si>
+    <t>15/09/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>6175524146</t>
+  </si>
+  <si>
+    <t>Desenvolver Aplicação Qlik Sense Dados Custeio</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>01/03/2024</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>9674221237</t>
+  </si>
+  <si>
+    <t>Projeto BI IROG SPA - Criar tela de cadastro de metas para BI</t>
+  </si>
+  <si>
+    <t>25/07/2025</t>
+  </si>
+  <si>
+    <t>14/09/2025</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>9787771130</t>
+  </si>
+  <si>
+    <t>Precisamos que SPS conecte ao WMS</t>
+  </si>
+  <si>
+    <t>11/08/2025</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>9879627311</t>
+  </si>
+  <si>
+    <t>ABERTURA DE SALDO SETOR 597 X MOVIMENTAÇÃO SETOR 7299</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>11/09/2025</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>9879680337</t>
+  </si>
+  <si>
+    <t>ESTORNO DE MOVIMENTAÇÃO EM VÁRIAS SEQUÊNCIAS</t>
+  </si>
+  <si>
+    <t>08/09/2025</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>9928178448</t>
+  </si>
+  <si>
+    <t>Planilhão via Qlik sense</t>
+  </si>
+  <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>9984634388</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Painel ajustagem</t>
+  </si>
+  <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>9985287551</t>
+  </si>
+  <si>
+    <t>ACRESCENTAR NOS MOTIVOS DE PARADA - A DESCRIÇÃO: INSPETOR RETESTANDO PEÇA NA CABINE</t>
+  </si>
+  <si>
+    <t>9985419559</t>
+  </si>
+  <si>
+    <t>APONTAMENTO ELETRONICO UPR MESA REDONDA</t>
+  </si>
+  <si>
+    <t>17/09/2025</t>
+  </si>
+  <si>
+    <t>9985803107</t>
+  </si>
+  <si>
+    <t>Atualização das informações no BI</t>
+  </si>
+  <si>
+    <t>10007327100</t>
+  </si>
+  <si>
+    <t>Sistema de Panelas</t>
+  </si>
+  <si>
+    <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>18001888887</t>
+  </si>
+  <si>
+    <t>Projeto BI IROG SPA - Cópia  de metas de ano/mês</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>9984614243</t>
+  </si>
+  <si>
+    <t>Criar campo para gatilho de analise de causa raiz</t>
+  </si>
+  <si>
+    <t>9985278576</t>
+  </si>
+  <si>
+    <t>Inclusão de custo de máquina parada na origem de custo dos custos de manutenção</t>
+  </si>
+  <si>
+    <t>9985403029</t>
+  </si>
+  <si>
+    <t>Adicionar um campo HISTÓRICO</t>
+  </si>
+  <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
+    <t>9985858778</t>
+  </si>
+  <si>
+    <t>Ajuste no inventario WMS</t>
+  </si>
+  <si>
+    <t>10007327219</t>
+  </si>
+  <si>
+    <t>Sistema de cadastro - Reunião</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira (apresentação)</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>9787746026</t>
+  </si>
+  <si>
+    <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
+  </si>
+  <si>
+    <t>9889620228</t>
+  </si>
+  <si>
+    <t>SISTEMA DE ENSAIOS MECÂNICOS DE PEÇA - Analise</t>
+  </si>
+  <si>
+    <t>25/08/2025</t>
+  </si>
+  <si>
+    <t>10001993454</t>
+  </si>
+  <si>
+    <t>alterar informações de romaneio e quantidade (copy)</t>
+  </si>
+  <si>
+    <t>9787746394</t>
+  </si>
+  <si>
+    <t>MELHORIAS FLUXO 109 REVISÕES</t>
+  </si>
+  <si>
+    <t>10007327544</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>9879999159</t>
+  </si>
+  <si>
+    <t>LOG DE ALTERAÇÕES APONTAMNETO ELETRONICO</t>
+  </si>
+  <si>
+    <t>10001408139</t>
+  </si>
+  <si>
+    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
+  </si>
+  <si>
+    <t>9684140503</t>
+  </si>
+  <si>
+    <t>Baixa de Estoque de Embalagem Expedição</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>9880289707</t>
+  </si>
+  <si>
+    <t>Melhoria de copia de analise e processos</t>
+  </si>
+  <si>
+    <t>9889773982</t>
+  </si>
+  <si>
+    <t>Retirar de peças do deposito para versão WMS</t>
+  </si>
+  <si>
+    <t>9985915461</t>
+  </si>
+  <si>
+    <t>Revisão de Checklist CPC</t>
+  </si>
+  <si>
+    <t>10009209101</t>
+  </si>
+  <si>
+    <t>Verificar apontamentos com origem na solda - Não permitir Alterar</t>
+  </si>
+  <si>
+    <t>9984835576</t>
+  </si>
+  <si>
+    <t>MPO's eletrônicas acabamento</t>
+  </si>
+  <si>
+    <t>10001543534</t>
+  </si>
+  <si>
+    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
+  </si>
+  <si>
+    <t>10007641274</t>
+  </si>
+  <si>
+    <t>Controle de documentação de exportação</t>
+  </si>
+  <si>
+    <t>10010545047</t>
+  </si>
+  <si>
+    <t>HUB CHATBOT - FRONTEND</t>
+  </si>
+  <si>
+    <t>10001692941</t>
+  </si>
+  <si>
+    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
+  </si>
+  <si>
+    <t>10007481377</t>
+  </si>
+  <si>
+    <t>Conversão KB TOTO - Relatórios</t>
+  </si>
+  <si>
+    <t>32150</t>
+  </si>
+  <si>
+    <t>Inventario WMS - Registro de Ajuste de Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
+  </si>
+  <si>
+    <t>10007327614</t>
+  </si>
+  <si>
+    <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
+  </si>
+  <si>
+    <t>10030012008</t>
+  </si>
+  <si>
+    <t>Relação de aplicações WEB</t>
+  </si>
+  <si>
+    <t>9985893344</t>
+  </si>
+  <si>
+    <t>Opção para movimentar todas as sequências no setor</t>
+  </si>
+  <si>
+    <t>9880278290</t>
+  </si>
+  <si>
+    <t>PAINEL DE INFO PARADAS JATOS</t>
+  </si>
+  <si>
+    <t>10007327672</t>
+  </si>
+  <si>
+    <t>Integração de faturamentos com eventos</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Integração CRM - Tarefa para disparar integrações</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>24641</t>
-  </si>
-  <si>
-    <t>Desenvolver Aplicação Qlik Sense Dados Custeio</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>01/03/2024</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>32974</t>
-  </si>
-  <si>
-    <t>Projeto BI IROG SPA - Criar tela de cadastro de metas para BI</t>
-  </si>
-  <si>
-    <t>25/07/2025</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>32425</t>
-  </si>
-  <si>
-    <t>Precisamos que SPS conecte ao WMS</t>
-  </si>
-  <si>
-    <t>11/08/2025</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>33657</t>
-  </si>
-  <si>
-    <t>ABERTURA DE SALDO SETOR 597 X MOVIMENTAÇÃO SETOR 7299</t>
-  </si>
-  <si>
-    <t>22/08/2025</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>33594</t>
-  </si>
-  <si>
-    <t>ESTORNO DE MOVIMENTAÇÃO EM VÁRIAS SEQUÊNCIAS</t>
-  </si>
-  <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>31685</t>
-  </si>
-  <si>
-    <t>Planilhão via Qlik sense</t>
-  </si>
-  <si>
-    <t>29/08/2025</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>33932</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Painel ajustagem</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>33820</t>
-  </si>
-  <si>
-    <t>ACRESCENTAR NOS MOTIVOS DE PARADA - A DESCRIÇÃO: INSPETOR RETESTANDO PEÇA NA CABINE</t>
-  </si>
-  <si>
-    <t>33807</t>
-  </si>
-  <si>
-    <t>APONTAMENTO ELETRONICO UPR MESA REDONDA</t>
-  </si>
-  <si>
-    <t>33676</t>
-  </si>
-  <si>
-    <t>Atualização das informações no BI</t>
-  </si>
-  <si>
-    <t>33077</t>
-  </si>
-  <si>
-    <t>Sistema de Panelas</t>
-  </si>
-  <si>
-    <t>Projeto BI IROG SPA - Cópia  de metas de ano/mês</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>33933</t>
-  </si>
-  <si>
-    <t>Criar campo para gatilho de analise de causa raiz</t>
-  </si>
-  <si>
-    <t>33834</t>
-  </si>
-  <si>
-    <t>Inclusão de custo de máquina parada na origem de custo dos custos de manutenção</t>
-  </si>
-  <si>
-    <t>33811</t>
-  </si>
-  <si>
-    <t>Adicionar um campo HISTÓRICO</t>
-  </si>
-  <si>
-    <t>33628</t>
-  </si>
-  <si>
-    <t>Ajuste no inventario WMS</t>
-  </si>
-  <si>
-    <t>33304</t>
-  </si>
-  <si>
-    <t>Sistema de cadastro - Reunião</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira (apresentação)</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>25418</t>
-  </si>
-  <si>
-    <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
-  </si>
-  <si>
-    <t>31347</t>
-  </si>
-  <si>
-    <t>SISTEMA DE ENSAIOS MECÂNICOS DE PEÇA - Analise</t>
-  </si>
-  <si>
-    <t>25/08/2025</t>
-  </si>
-  <si>
-    <t>32077</t>
-  </si>
-  <si>
-    <t>alterar informações de romaneio e quantidade (copy)</t>
-  </si>
-  <si>
-    <t>08/09/2025</t>
-  </si>
-  <si>
-    <t>31270</t>
-  </si>
-  <si>
-    <t>MELHORIAS FLUXO 109 REVISÕES</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>33492</t>
-  </si>
-  <si>
-    <t>LOG DE ALTERAÇÕES APONTAMNETO ELETRONICO</t>
-  </si>
-  <si>
-    <t>32723</t>
-  </si>
-  <si>
-    <t>Viabilidade e Proposta - Retificação de SPED Fiscal</t>
-  </si>
-  <si>
-    <t>32588</t>
-  </si>
-  <si>
-    <t>Baixa de Estoque de Embalagem Expedição</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>33441</t>
-  </si>
-  <si>
-    <t>Melhoria de copia de analise e processos</t>
-  </si>
-  <si>
-    <t>26571</t>
-  </si>
-  <si>
-    <t>Retirar de peças do deposito para versão WMS</t>
-  </si>
-  <si>
-    <t>33571</t>
-  </si>
-  <si>
-    <t>Revisão de Checklist CPC</t>
-  </si>
-  <si>
-    <t>33333</t>
-  </si>
-  <si>
-    <t>Verificar apontamentos com origem na solda - Não permitir Alterar</t>
-  </si>
-  <si>
-    <t>33896</t>
-  </si>
-  <si>
-    <t>MPO's eletrônicas acabamento</t>
-  </si>
-  <si>
-    <t>32685</t>
-  </si>
-  <si>
-    <t>Qlik - Vinculo de Atualização Comparação de volume</t>
-  </si>
-  <si>
-    <t>33662</t>
-  </si>
-  <si>
-    <t>Controle de documentação de exportação</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>HUB CHATBOT - FRONTEND</t>
-  </si>
-  <si>
-    <t>29476</t>
-  </si>
-  <si>
-    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
-  </si>
-  <si>
-    <t>31015</t>
-  </si>
-  <si>
-    <t>Conversão KB TOTO - Relatórios</t>
-  </si>
-  <si>
-    <t>32150</t>
-  </si>
-  <si>
-    <t>Inventario WMS - Registro de Ajuste de Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Maciel, Quando realizamos o Inventario no WMS, ele faz a comparação dos estoques. Porém conforme o pessoal faz o inventario, eles fazem o ajuste do box. Eu preciso que no e-mail que baixamos do Inventario, uma aba conste todos os romaneios lidos com número de modelo, liga e quantidade, e </t>
-  </si>
-  <si>
-    <t>33519</t>
-  </si>
-  <si>
-    <t>Backlog de alterações - Sistema Manutenção -&gt; SS e OS</t>
-  </si>
-  <si>
-    <t>Relação de aplicações WEB</t>
-  </si>
-  <si>
-    <t>11/09/2025</t>
-  </si>
-  <si>
-    <t>33592</t>
-  </si>
-  <si>
-    <t>Opção para movimentar todas as sequências no setor</t>
-  </si>
-  <si>
-    <t>33445</t>
-  </si>
-  <si>
-    <t>PAINEL DE INFO PARADAS JATOS</t>
-  </si>
-  <si>
-    <t>24746</t>
-  </si>
-  <si>
-    <t>Integração de faturamentos com eventos</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Integração CRM - Tarefa para disparar integrações</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>33516</t>
+    <t>10007327741</t>
   </si>
   <si>
     <t>Melhoria no sistema de cadastro de modelos, no histórico de conserto de modelos</t>
   </si>
   <si>
-    <t>33618</t>
+    <t>10007171031</t>
   </si>
   <si>
     <t>Bloco K - Ajuste no filtro de seleção das sequências oriundas do cálculo do custo.</t>
   </si>
   <si>
-    <t>33244</t>
+    <t>9889920491</t>
   </si>
   <si>
     <t>Integração do mapeamento digital com sistema do PCP</t>
   </si>
   <si>
-    <t>33023</t>
+    <t>10007218134</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -489,61 +513,67 @@
     <t>Integração CRM - Carga Ofertas</t>
   </si>
   <si>
-    <t>31609</t>
+    <t>9889620409</t>
   </si>
   <si>
     <t>ALERTA DE REVISÃO X BLOQUEIO DE MODELO</t>
   </si>
   <si>
-    <t>33773</t>
+    <t>9985547053</t>
   </si>
   <si>
     <t>Alteração na aplicação do CPP</t>
   </si>
   <si>
-    <t>33793</t>
+    <t>9985485519</t>
   </si>
   <si>
     <t>PAINEL DE PARADAS MANIPULADORES</t>
   </si>
   <si>
-    <t>33794</t>
+    <t>9985459250</t>
   </si>
   <si>
     <t>Melhoria B.I - Análise</t>
   </si>
   <si>
+    <t>10006673745</t>
+  </si>
+  <si>
     <t>Validar apontamentos com longos períodos.</t>
   </si>
   <si>
+    <t>10007480787</t>
+  </si>
+  <si>
     <t>HUB CHATBOT - API</t>
   </si>
   <si>
-    <t>33772</t>
+    <t>9985555265</t>
   </si>
   <si>
     <t>Melhoria no cadastramento dos tempos padrões - CPP</t>
   </si>
   <si>
-    <t>33009</t>
+    <t>10007480716</t>
   </si>
   <si>
     <t>Controle de indicadores ao vivo</t>
   </si>
   <si>
-    <t>33914</t>
+    <t>9984685143</t>
   </si>
   <si>
     <t>Centro de custo</t>
   </si>
   <si>
-    <t>33554</t>
+    <t>9986002527</t>
   </si>
   <si>
     <t>Melhoria no sistema de baixa de EPI</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>10007377633</t>
   </si>
   <si>
     <t>Novo Sistema</t>
@@ -552,43 +582,43 @@
     <t>Incluir numero da Tag - campo texto</t>
   </si>
   <si>
-    <t>33884</t>
+    <t>9984855176</t>
   </si>
   <si>
     <t>Altona || Importação de fretes - Diferença de valor - Trava Integrator</t>
   </si>
   <si>
-    <t>33757</t>
+    <t>9985573486</t>
   </si>
   <si>
     <t>Corrigir erro - compara carteira</t>
   </si>
   <si>
-    <t>33755</t>
+    <t>9985580747</t>
   </si>
   <si>
     <t>Qlik- Base de recibo de Embarque Parcial</t>
   </si>
   <si>
-    <t>33412</t>
+    <t>10007218620</t>
   </si>
   <si>
     <t>Atualização de Metas</t>
   </si>
   <si>
-    <t>33722</t>
+    <t>9985639994</t>
   </si>
   <si>
     <t>Abertura de Ordens de Serviço</t>
   </si>
   <si>
-    <t>32404</t>
+    <t>10007218477</t>
   </si>
   <si>
     <t>BI para análises das auditorias de CIPA</t>
   </si>
   <si>
-    <t>27379</t>
+    <t>10008593080</t>
   </si>
   <si>
     <t>Calculo do custo de embalagens</t>
@@ -597,13 +627,13 @@
     <t>Impedimento</t>
   </si>
   <si>
-    <t>33744</t>
+    <t>9985607008</t>
   </si>
   <si>
     <t>Adição filtro solicitante</t>
   </si>
   <si>
-    <t>33878</t>
+    <t>9985031244</t>
   </si>
   <si>
     <t>Gráfico de Kg de eletrodo por tonelada de peça produzida</t>
@@ -621,55 +651,55 @@
     <t>Jacson Schneider Movidesk</t>
   </si>
   <si>
-    <t>33599</t>
+    <t>10007218856</t>
   </si>
   <si>
     <t>Aplicação Insertos Usinagem</t>
   </si>
   <si>
-    <t>33521</t>
+    <t>9986018528</t>
   </si>
   <si>
     <t>APLICAÇÃO IROG ACABAMENTO (REBARBAÇÃO MANIPULADOR)</t>
   </si>
   <si>
-    <t>33870</t>
+    <t>9985068283</t>
   </si>
   <si>
     <t>Alteração follow up de pedidos compras</t>
   </si>
   <si>
-    <t>33869</t>
+    <t>9985079775</t>
   </si>
   <si>
     <t>Solda</t>
   </si>
   <si>
-    <t>33961</t>
+    <t>9986611061</t>
   </si>
   <si>
     <t>TEMPOS ZERADOS - MODELOS UPR</t>
   </si>
   <si>
-    <t>29123</t>
+    <t>10007218730</t>
   </si>
   <si>
     <t>B.I ordens de manutenção maquinas pneumáticas</t>
   </si>
   <si>
-    <t>33895</t>
+    <t>10009091500</t>
   </si>
   <si>
     <t>ERRO: Sistema de Corridas - Planilha Custeio MP</t>
   </si>
   <si>
-    <t>33875</t>
+    <t>9985056102</t>
   </si>
   <si>
     <t>Altona || Conferência Entrada de Consignados</t>
   </si>
   <si>
-    <t>33963</t>
+    <t>9992905368</t>
   </si>
   <si>
     <t>Publicar aplicações de apontamento (POSTMOVTO)</t>
@@ -678,112 +708,112 @@
     <t>07/09/2025</t>
   </si>
   <si>
-    <t>33921</t>
+    <t>9984660366</t>
   </si>
   <si>
     <t>Carteira Sense</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>10007170520</t>
   </si>
   <si>
     <t>Consulta de divergências - Registro Pintura</t>
   </si>
   <si>
-    <t>32677</t>
+    <t>10007170942</t>
   </si>
   <si>
     <t>PDI - Fixar colunas de identificação das cotas</t>
   </si>
   <si>
-    <t>32353</t>
+    <t>10007170704</t>
   </si>
   <si>
     <t>Melhoria Sistema de Custeio - Usinagem Pintura - Revisão de Calculo</t>
   </si>
   <si>
-    <t xml:space="preserve">Alexandre, bom dia! Para Custeio Usinagem Pintura, ao invés de utilizar apontamentos de horas, valores do setor PINTURA (centro custo 8010) devem ser rateados somente para as sequências movimentadas no setor 3081. Critério de rateio deve ser proporcional de custo FTF dos setores 3081 + 3082 + 8010. </t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>30903</t>
+    <t>10007170458</t>
   </si>
   <si>
     <t>Controle do status por declaração</t>
   </si>
   <si>
-    <t>33713</t>
+    <t>9985687134</t>
   </si>
   <si>
     <t>Incluir informação - Sequencia</t>
   </si>
   <si>
-    <t>33694</t>
+    <t>9985782356</t>
   </si>
   <si>
     <t>Ajustas layout do BI da Moldagem</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>10007219132</t>
   </si>
   <si>
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião</t>
   </si>
   <si>
+    <t>10007170598</t>
+  </si>
+  <si>
     <t>PDI - Inspeção - Cotas informadas.</t>
   </si>
   <si>
-    <t>33867</t>
+    <t>9985109263</t>
   </si>
   <si>
     <t>Arvore de ativos na WEB</t>
   </si>
   <si>
-    <t>33331</t>
+    <t>20/09/2025</t>
+  </si>
+  <si>
+    <t>10007290594</t>
   </si>
   <si>
     <t>Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
   </si>
   <si>
-    <t>33691</t>
+    <t>9985744680</t>
   </si>
   <si>
     <t>Painel de prazo de lançamento de notas</t>
   </si>
   <si>
-    <t>33288</t>
+    <t>10007219013</t>
   </si>
   <si>
     <t>FTF Qualidade</t>
   </si>
   <si>
-    <t>33855</t>
+    <t>9985198318</t>
   </si>
   <si>
     <t>PMOV</t>
   </si>
   <si>
-    <t>33401</t>
+    <t>10007218943</t>
   </si>
   <si>
     <t>Gráfico refugo diário - SENSE</t>
   </si>
   <si>
-    <t>33860</t>
+    <t>9985141390</t>
   </si>
   <si>
     <t>Altona || Exportação OSI - Melhoria</t>
   </si>
   <si>
-    <t>33271</t>
+    <t>10007290776</t>
   </si>
   <si>
     <t>Extração de dados IROG Usinagem</t>
   </si>
   <si>
-    <t>32536</t>
+    <t>10007290895</t>
   </si>
   <si>
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
@@ -825,6 +855,9 @@
     <t>Apontamento de moldes Carrossel</t>
   </si>
   <si>
+    <t>10032493777</t>
+  </si>
+  <si>
     <t>Interface para o usuário realizar a integração com OpCenter</t>
   </si>
   <si>
@@ -834,7 +867,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-19</t>
+    <t>Mar/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1467,7 +1500,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
@@ -1514,7 +1547,7 @@
         <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>33</v>
@@ -1523,15 +1556,15 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1543,10 +1576,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1558,7 +1591,7 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
@@ -1573,59 +1606,59 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1637,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1652,27 +1685,27 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1684,10 +1717,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1699,10 +1732,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>33</v>
@@ -1711,30 +1744,30 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1746,10 +1779,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>33</v>
@@ -1766,7 +1799,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1778,25 +1811,25 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>33</v>
@@ -1813,7 +1846,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1825,10 +1858,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1840,10 +1873,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>33</v>
@@ -1860,7 +1893,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1872,10 +1905,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1887,10 +1920,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>33</v>
@@ -1907,7 +1940,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1919,10 +1952,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1937,7 +1970,7 @@
         <v>23</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1954,7 +1987,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1966,10 +1999,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1981,10 +2014,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>33</v>
@@ -1993,7 +2026,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -2001,7 +2034,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -2013,10 +2046,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -2028,16 +2061,16 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>34</v>
@@ -2048,7 +2081,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -2060,10 +2093,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -2075,16 +2108,16 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>34</v>
@@ -2095,7 +2128,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -2107,10 +2140,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -2122,10 +2155,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>33</v>
@@ -2142,7 +2175,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -2154,10 +2187,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2169,10 +2202,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>33</v>
@@ -2189,7 +2222,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -2201,10 +2234,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -2219,7 +2252,7 @@
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>33</v>
@@ -2236,37 +2269,37 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -2275,7 +2308,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O20" s="2" t="s">
         <v>28</v>
@@ -2283,7 +2316,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2295,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2310,27 +2343,27 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2342,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -2357,10 +2390,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>33</v>
@@ -2369,15 +2402,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2389,10 +2422,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2404,7 +2437,7 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -2424,7 +2457,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2436,10 +2469,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2451,27 +2484,27 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2483,10 +2516,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2501,7 +2534,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2518,7 +2551,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2530,10 +2563,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2545,10 +2578,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>33</v>
@@ -2557,15 +2590,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2577,10 +2610,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2592,10 +2625,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>33</v>
@@ -2612,7 +2645,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2624,10 +2657,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2639,10 +2672,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2651,15 +2684,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2671,10 +2704,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2686,27 +2719,27 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2718,10 +2751,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2733,10 +2766,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2745,15 +2778,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2765,10 +2798,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2780,7 +2813,7 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -2800,7 +2833,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2812,10 +2845,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2830,7 +2863,7 @@
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2847,7 +2880,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2859,10 +2892,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2874,7 +2907,7 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>24</v>
@@ -2894,7 +2927,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2906,10 +2939,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2921,16 +2954,16 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>27</v>
@@ -2941,7 +2974,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2953,10 +2986,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2971,7 +3004,7 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>33</v>
@@ -2988,7 +3021,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -3000,10 +3033,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -3018,7 +3051,7 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>33</v>
@@ -3035,7 +3068,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -3047,10 +3080,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -3062,16 +3095,16 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>97</v>
+        <v>53</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -3082,22 +3115,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -3112,13 +3145,13 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -3129,37 +3162,37 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K39" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>33</v>
@@ -3176,7 +3209,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -3188,10 +3221,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3206,13 +3239,13 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>27</v>
@@ -3223,22 +3256,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -3250,10 +3283,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>33</v>
@@ -3270,7 +3303,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -3282,10 +3315,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3297,10 +3330,10 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>33</v>
@@ -3317,7 +3350,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3329,10 +3362,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -3344,10 +3377,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>33</v>
@@ -3356,30 +3389,30 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3394,13 +3427,13 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -3411,43 +3444,43 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>27</v>
@@ -3458,7 +3491,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3470,10 +3503,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3488,7 +3521,7 @@
         <v>23</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3505,7 +3538,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3517,10 +3550,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3535,7 +3568,7 @@
         <v>23</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>33</v>
@@ -3552,7 +3585,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3564,10 +3597,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3579,42 +3612,42 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
@@ -3629,13 +3662,13 @@
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>27</v>
@@ -3646,43 +3679,43 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
@@ -3693,7 +3726,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3705,10 +3738,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3720,10 +3753,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3732,15 +3765,15 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3752,10 +3785,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3767,10 +3800,10 @@
         <v>22</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>33</v>
@@ -3787,7 +3820,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3799,10 +3832,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3814,10 +3847,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3834,7 +3867,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3846,10 +3879,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -3861,10 +3894,10 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>33</v>
@@ -3881,7 +3914,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3893,10 +3926,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3911,7 +3944,7 @@
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3928,7 +3961,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3940,10 +3973,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3958,7 +3991,7 @@
         <v>23</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>33</v>
@@ -3975,7 +4008,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3987,10 +4020,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
@@ -4002,16 +4035,16 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>34</v>
@@ -4022,7 +4055,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -4034,10 +4067,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
@@ -4069,7 +4102,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -4081,10 +4114,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -4096,10 +4129,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>33</v>
@@ -4116,7 +4149,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -4128,10 +4161,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4143,10 +4176,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>33</v>
@@ -4163,22 +4196,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4193,7 +4226,7 @@
         <v>23</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>33</v>
@@ -4210,7 +4243,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -4222,10 +4255,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4237,10 +4270,10 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>33</v>
@@ -4257,22 +4290,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4284,10 +4317,10 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>33</v>
@@ -4304,7 +4337,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -4316,10 +4349,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4331,10 +4364,10 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>33</v>
@@ -4351,7 +4384,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4363,10 +4396,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4381,13 +4414,13 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>27</v>
@@ -4398,7 +4431,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4410,10 +4443,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4425,10 +4458,10 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>33</v>
@@ -4445,22 +4478,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>31</v>
@@ -4478,10 +4511,10 @@
         <v>24</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>27</v>
@@ -4492,7 +4525,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4504,10 +4537,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
@@ -4522,13 +4555,13 @@
         <v>23</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>27</v>
@@ -4539,7 +4572,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4551,10 +4584,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
@@ -4566,10 +4599,10 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>33</v>
@@ -4586,7 +4619,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4598,10 +4631,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4613,16 +4646,16 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>34</v>
@@ -4633,43 +4666,43 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>27</v>
@@ -4680,22 +4713,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4710,13 +4743,13 @@
         <v>23</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>27</v>
@@ -4727,7 +4760,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
@@ -4739,10 +4772,10 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4754,10 +4787,10 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>33</v>
@@ -4774,7 +4807,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
@@ -4786,10 +4819,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4801,10 +4834,10 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>33</v>
@@ -4821,7 +4854,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>16</v>
@@ -4833,10 +4866,10 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4848,10 +4881,10 @@
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>33</v>
@@ -4868,7 +4901,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
@@ -4880,10 +4913,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4895,10 +4928,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>33</v>
@@ -4915,7 +4948,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
@@ -4927,10 +4960,10 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4945,13 +4978,13 @@
         <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>27</v>
@@ -4962,22 +4995,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -5009,7 +5042,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
@@ -5021,10 +5054,10 @@
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -5036,10 +5069,10 @@
         <v>22</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>33</v>
@@ -5056,7 +5089,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
@@ -5068,10 +5101,10 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>31</v>
@@ -5083,10 +5116,10 @@
         <v>22</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>33</v>
@@ -5103,22 +5136,22 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5130,10 +5163,10 @@
         <v>22</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>33</v>
@@ -5150,7 +5183,7 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
@@ -5162,10 +5195,10 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5183,10 +5216,10 @@
         <v>24</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>27</v>
@@ -5197,7 +5230,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
@@ -5209,10 +5242,10 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5227,13 +5260,13 @@
         <v>23</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>27</v>
@@ -5244,7 +5277,7 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
@@ -5253,34 +5286,34 @@
         <v>17</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>27</v>
@@ -5291,22 +5324,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5321,13 +5354,13 @@
         <v>23</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>27</v>
@@ -5338,7 +5371,7 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
@@ -5350,10 +5383,10 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5365,16 +5398,16 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>34</v>
@@ -5385,7 +5418,7 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
@@ -5397,10 +5430,10 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5412,10 +5445,10 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>33</v>
@@ -5432,22 +5465,22 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5462,13 +5495,13 @@
         <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>27</v>
@@ -5479,7 +5512,7 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
@@ -5491,10 +5524,10 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5509,13 +5542,13 @@
         <v>23</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>27</v>
@@ -5526,7 +5559,7 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
@@ -5538,10 +5571,10 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5553,16 +5586,16 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>251</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>34</v>
@@ -5573,7 +5606,7 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
@@ -5585,10 +5618,10 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5603,13 +5636,13 @@
         <v>23</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>27</v>
@@ -5620,7 +5653,7 @@
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
@@ -5632,10 +5665,10 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5647,10 +5680,10 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>33</v>
@@ -5667,22 +5700,22 @@
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>20</v>
@@ -5697,7 +5730,7 @@
         <v>23</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>33</v>
@@ -5714,7 +5747,7 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>16</v>
@@ -5726,10 +5759,10 @@
         <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
@@ -5741,16 +5774,16 @@
         <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>34</v>
@@ -5761,7 +5794,7 @@
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>16</v>
@@ -5773,10 +5806,10 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
@@ -5791,13 +5824,13 @@
         <v>23</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -5808,7 +5841,7 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>16</v>
@@ -5820,10 +5853,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -5835,10 +5868,10 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>33</v>
@@ -5855,7 +5888,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>16</v>
@@ -5867,10 +5900,10 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>20</v>
@@ -5885,13 +5918,13 @@
         <v>23</v>
       </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>27</v>
@@ -5902,7 +5935,7 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>16</v>
@@ -5914,10 +5947,10 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>20</v>
@@ -5932,13 +5965,13 @@
         <v>23</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
         <v>27</v>
@@ -5949,43 +5982,43 @@
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M99" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
         <v>27</v>
@@ -5996,43 +6029,43 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>16</v>
+        <v>90</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K100" s="2" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="L100" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>27</v>
@@ -6043,7 +6076,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>16</v>
@@ -6055,10 +6088,10 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>20</v>
@@ -6070,16 +6103,16 @@
         <v>22</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>34</v>
@@ -6090,22 +6123,22 @@
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>63</v>
+        <v>280</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>31</v>
@@ -6117,16 +6150,16 @@
         <v>22</v>
       </c>
       <c r="J102" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="K102" s="2" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L102" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M102" s="2" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="N102" s="2" t="s">
         <v>27</v>
@@ -6148,23 +6181,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B2" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D2" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E2" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6172,16 +6205,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6192,15 +6225,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>248</v>
+        <v>26.87</v>
       </c>
       <c r="J5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6221,7 +6254,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6252,12 +6285,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B2">
         <v>101</v>
@@ -6271,35 +6304,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>248</v>
+        <v>26.87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -6307,7 +6340,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -6316,13 +6349,13 @@
         <v>82</v>
       </c>
       <c r="G10" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -6334,21 +6367,21 @@
         <v>46</v>
       </c>
       <c r="P10" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>90</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E11">
         <v>8</v>
@@ -6363,30 +6396,30 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="M11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N11">
         <v>30</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="Q11">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>150</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -6398,59 +6431,53 @@
         <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="K12">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="N12">
         <v>1</v>
       </c>
-      <c r="P12" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N13">
         <v>6</v>
       </c>
-      <c r="P13" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="4:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D14" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E14">
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -6461,16 +6488,10 @@
       <c r="N14">
         <v>14</v>
       </c>
-      <c r="P14" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q14">
-        <v>1</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N15">
         <v>4</v>
@@ -6478,7 +6499,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -6486,7 +6507,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -6494,10 +6515,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -6505,7 +6526,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -6513,142 +6534,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>238</v>
+        <v>824</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>228</v>
+        <v>824</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
